--- a/ftmn/FTM-N03/2026-10-20_suivi-contacts-ventes-marketing.xlsx
+++ b/ftmn/FTM-N03/2026-10-20_suivi-contacts-ventes-marketing.xlsx
@@ -705,7 +705,7 @@
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>Non abordé</t>
+          <t>6 à 12 mois</t>
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="P6" s="5" t="inlineStr">
         <is>
-          <t>Rendez-vous pris</t>
+          <t>Visite faite</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>+225 07 •• •• •• 52</t>
+          <t>+225 07 •• •• •• 60</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Jardins d’Ahoué</t>
+          <t>Résidences Kotibé</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui, déclaré</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
@@ -940,12 +940,12 @@
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>Plus de 12 mois</t>
+          <t>6 à 12 mois</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>Non abordé</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="O9" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>+225 07 •• •• •• 13</t>
+          <t>+225 07 •• •• •• 26</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -999,12 +999,12 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>Résidences Kotibé</t>
+          <t>Non précisé</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>Simple information prix</t>
+          <t>Achat résidence principale</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
@@ -1019,12 +1019,12 @@
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
+          <t>Plus de 12 mois</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
           <t>Non abordé</t>
-        </is>
-      </c>
-      <c r="K10" s="5" t="inlineStr">
-        <is>
-          <t>Oui</t>
         </is>
       </c>
       <c r="L10" s="5" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Didier D. (fictif)</t>
+          <t>Didier C. (fictif)</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>manquant</t>
+          <t>+225 07 •• •• •• 37</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>Plus de 12 mois</t>
+          <t>6 à 12 mois</t>
         </is>
       </c>
       <c r="K12" s="5" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="P12" s="5" t="inlineStr">
         <is>
-          <t>Rendu : numéro faux</t>
+          <t>Réservation</t>
         </is>
       </c>
     </row>
@@ -1375,12 +1375,12 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Christelle D. (fictif)</t>
+          <t>Christelle G. (fictif)</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>+225 07 •• •• •• 51</t>
+          <t>+225 07 •• •• •• 75</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -1395,12 +1395,12 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>Simple information prix</t>
+          <t>Achat résidence principale</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui, déclaré</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
@@ -1429,13 +1429,15 @@
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="O15" s="4" t="inlineStr"/>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="O15" s="4" t="n">
+        <v>8</v>
+      </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>Gardé au marketing</t>
+          <t>Réservation</t>
         </is>
       </c>
     </row>
@@ -1452,12 +1454,12 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Ibrahim A. (fictif)</t>
+          <t>Ibrahim T. (fictif)</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>+225 07 •• •• •• 89</t>
+          <t>+225 07 •• •• •• 16</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -1467,17 +1469,17 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>Non précisé</t>
+          <t>Jardins d’Ahoué</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>Achat résidence principale</t>
+          <t>Simple information prix</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>Oui, déclaré</t>
+          <t>Non</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
@@ -1487,7 +1489,7 @@
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>Plus de 12 mois</t>
+          <t>6 à 12 mois</t>
         </is>
       </c>
       <c r="K16" s="5" t="inlineStr">
@@ -1529,12 +1531,12 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Josiane D. (fictif)</t>
+          <t>Josiane T. (fictif)</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>+225 07 •• •• •• 99</t>
+          <t>manquant</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -1544,7 +1546,7 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Jardins d’Ahoué</t>
+          <t>Résidences Kotibé</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
@@ -1564,7 +1566,7 @@
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>Plus de 12 mois</t>
+          <t>6 à 12 mois</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
@@ -1606,12 +1608,12 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Kouamé T. (fictif)</t>
+          <t>Kouamé A. (fictif)</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>+225 07 •• •• •• 56</t>
+          <t>+225 07 •• •• •• 27</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -1621,12 +1623,12 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>Jardins d’Ahoué</t>
+          <t>Résidences Kotibé</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>Simple information prix</t>
+          <t>Achat résidence principale</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
@@ -1641,17 +1643,17 @@
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>Non abordé</t>
+          <t>Moins de 6 mois</t>
         </is>
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>Non abordé</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>Non noté</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="M18" s="5">
@@ -1664,11 +1666,11 @@
         </is>
       </c>
       <c r="O18" s="5" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="P18" s="5" t="inlineStr">
         <is>
-          <t>Rendez-vous pris</t>
+          <t>Réservation</t>
         </is>
       </c>
     </row>
@@ -1685,12 +1687,12 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Salimata B. (fictif)</t>
+          <t>Salimata G. (fictif)</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>+225 07 •• •• •• 29</t>
+          <t>+225 07 •• •• •• 61</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -1705,32 +1707,32 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>Simple information prix</t>
+          <t>Achat résidence principale</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>Oui, déclaré</t>
+          <t>Non</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
+          <t>Fonds propres</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>Moins de 6 mois</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
           <t>Non abordé</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>6 à 12 mois</t>
-        </is>
-      </c>
-      <c r="K19" s="4" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>Non noté</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="M19" s="4">
@@ -1739,15 +1741,13 @@
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="O19" s="4" t="n">
-        <v>12</v>
-      </c>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="O19" s="4" t="inlineStr"/>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>Rendu : budget inconnu</t>
+          <t>Gardé au marketing</t>
         </is>
       </c>
     </row>
@@ -1789,7 +1789,7 @@
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui, déclaré</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
@@ -1799,12 +1799,12 @@
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>6 à 12 mois</t>
+          <t>Moins de 6 mois</t>
         </is>
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
-          <t>Oui</t>
+          <t>Non (conjoint)</t>
         </is>
       </c>
       <c r="L20" s="5" t="inlineStr">
@@ -1821,14 +1821,12 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="O20" s="5" t="inlineStr">
-        <is>
-          <t>non rappelé</t>
-        </is>
+      <c r="O20" s="5" t="n">
+        <v>1</v>
       </c>
       <c r="P20" s="5" t="inlineStr">
         <is>
-          <t>Jamais rappelé</t>
+          <t>Rendez-vous pris</t>
         </is>
       </c>
     </row>
@@ -1944,7 +1942,7 @@
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>Simple information prix</t>
+          <t>Achat résidence principale</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
@@ -1986,7 +1984,7 @@
       </c>
       <c r="P22" s="5" t="inlineStr">
         <is>
-          <t>Rendu : simple curieux</t>
+          <t>Réservation</t>
         </is>
       </c>
     </row>
@@ -2240,12 +2238,12 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Franck G. (fictif)</t>
+          <t>Franck Y. (fictif)</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>manquant</t>
+          <t>+225 07 •• •• •• 51</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -2255,7 +2253,7 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>Non précisé</t>
+          <t>Résidences Kotibé</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
@@ -2275,7 +2273,7 @@
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>Plus de 12 mois</t>
+          <t>Moins de 6 mois</t>
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr">
@@ -2297,12 +2295,14 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="O26" s="5" t="n">
-        <v>8</v>
+      <c r="O26" s="5" t="inlineStr">
+        <is>
+          <t>non rappelé</t>
+        </is>
       </c>
       <c r="P26" s="5" t="inlineStr">
         <is>
-          <t>Rendu : numéro faux</t>
+          <t>Jamais rappelé</t>
         </is>
       </c>
     </row>
@@ -2324,7 +2324,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>manquant</t>
+          <t>+225 07 •• •• •• 16</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>Jardins d’Ahoué</t>
+          <t>Non précisé</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Djénéba O. (fictif)</t>
+          <t>Djénéba G. (fictif)</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>+225 07 •• •• •• 74</t>
+          <t>+225 07 •• •• •• 35</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>Résidences Kotibé</t>
+          <t>Non précisé</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
@@ -2658,7 +2658,7 @@
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui, déclaré</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
@@ -2668,7 +2668,7 @@
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>6 à 12 mois</t>
+          <t>Moins de 6 mois</t>
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>Rendu : simple curieux</t>
+          <t>Visite faite</t>
         </is>
       </c>
     </row>
@@ -2712,12 +2712,12 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>Patrick D. (fictif)</t>
+          <t>Patrick B. (fictif)</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>+225 07 •• •• •• 85</t>
+          <t>+225 07 •• •• •• 12</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -2727,27 +2727,27 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>Résidences Kotibé</t>
+          <t>Non précisé</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Investissement locatif</t>
+          <t>Simple information prix</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>Oui, déclaré</t>
+          <t>Non</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>Fonds propres</t>
+          <t>Non abordé</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>Non abordé</t>
+          <t>6 à 12 mois</t>
         </is>
       </c>
       <c r="K32" s="5" t="inlineStr">
@@ -2766,15 +2766,13 @@
       </c>
       <c r="N32" s="5" t="inlineStr">
         <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="O32" s="5" t="n">
-        <v>2</v>
-      </c>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="O32" s="5" t="inlineStr"/>
       <c r="P32" s="5" t="inlineStr">
         <is>
-          <t>Rendu : simple curieux</t>
+          <t>Gardé au marketing</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2789,12 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Edwige A. (fictif)</t>
+          <t>Edwige K. (fictif)</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>manquant</t>
+          <t>+225 07 •• •• •• 86</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
@@ -2806,7 +2804,7 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>Jardins d’Ahoué</t>
+          <t>Non précisé</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
@@ -2821,7 +2819,7 @@
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>Non abordé</t>
+          <t>Fonds propres</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -2831,7 +2829,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>Non abordé</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
@@ -2845,15 +2843,13 @@
       </c>
       <c r="N33" s="4" t="inlineStr">
         <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="O33" s="4" t="n">
-        <v>1</v>
-      </c>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="O33" s="4" t="inlineStr"/>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>Rendez-vous pris</t>
+          <t>Gardé au marketing</t>
         </is>
       </c>
     </row>
@@ -2870,12 +2866,12 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>Souleymane G. (fictif)</t>
+          <t>Souleymane A. (fictif)</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>+225 07 •• •• •• 13</t>
+          <t>+225 07 •• •• •• 22</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -2885,12 +2881,12 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>Jardins d’Ahoué</t>
+          <t>Résidences Kotibé</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>Achat résidence principale</t>
+          <t>Investissement locatif</t>
         </is>
       </c>
       <c r="H34" s="5" t="inlineStr">
@@ -2900,22 +2896,22 @@
       </c>
       <c r="I34" s="5" t="inlineStr">
         <is>
-          <t>Prêt bancaire en cours</t>
+          <t>Non abordé</t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>Non abordé</t>
+          <t>6 à 12 mois</t>
         </is>
       </c>
       <c r="K34" s="5" t="inlineStr">
         <is>
-          <t>Non abordé</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>Oui</t>
+          <t>Non noté</t>
         </is>
       </c>
       <c r="M34" s="5">
@@ -2928,11 +2924,11 @@
         </is>
       </c>
       <c r="O34" s="5" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="P34" s="5" t="inlineStr">
         <is>
-          <t>Rendez-vous pris</t>
+          <t>Rendu : simple curieux</t>
         </is>
       </c>
     </row>
